--- a/backup_tf_files/false_negative_priority.xlsx
+++ b/backup_tf_files/false_negative_priority.xlsx
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="F149" s="2" t="n">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>lfi</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>lfi</t>
         </is>
       </c>
       <c r="F154" s="2" t="n">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>lfi</t>
         </is>
       </c>
       <c r="F155" s="2" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>lfi</t>
         </is>
       </c>
       <c r="F156" s="2" t="n">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>xss</t>
+          <t>lfi</t>
         </is>
       </c>
       <c r="F181" s="2" t="n">
@@ -6712,6 +6712,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -6784,6 +6785,8 @@
         <v>186</v>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
@@ -6828,13 +6831,13 @@
         <v>41</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -6859,58 +6862,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rfi</t>
+          <t>cmdi</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ssti</t>
+          <t>rfi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cmdi</t>
+          <t>ssti</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -6923,13 +6926,13 @@
         <v>0</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
